--- a/ProblemSolving/FINAL450.xlsx
+++ b/ProblemSolving/FINAL450.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Algorithm\ProblemSolving\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222BC6A1-E713-4872-A005-01FC9B898F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9D2298-1A50-4E8B-975C-A8ED41EA2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="472">
   <si>
     <t>Questions by Love Babbar:</t>
   </si>
@@ -1441,6 +1441,12 @@
   </si>
   <si>
     <t>https://github.com/ritam-sarkar/Algorithm/blob/master/ProblemSolving/src/com/orcl/array/DuthFlagProblem.java</t>
+  </si>
+  <si>
+    <t>https://github.com/ritam-sarkar/Algorithm/blob/master/ProblemSolving/src/com/orcl/search/FindMedianSortedArray.java</t>
+  </si>
+  <si>
+    <t>https://github.com/ritam-sarkar/Algorithm/blob/master/ProblemSolving/src/com/orcl/search/FindKthElementOfTwoSortedArray.java</t>
   </si>
 </sst>
 </file>
@@ -1883,15 +1889,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CDA779-6CF2-8045-9DE0-880424A4EED5}">
   <dimension ref="A1:D481"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
     <col min="2" max="2" width="123" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="72.6640625" customWidth="1"/>
+    <col min="4" max="4" width="72.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25">
+    <row r="1" spans="1:4" ht="26.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1920,7 +1926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="32.5">
+    <row r="6" spans="1:4" ht="33">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1945,7 +1951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="48">
+    <row r="8" spans="1:4" ht="48.75">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1959,7 +1965,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="48">
+    <row r="9" spans="1:4" ht="48.75">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
@@ -2226,7 +2232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="21">
+    <row r="33" spans="1:4" ht="21">
       <c r="A33" s="5" t="s">
         <v>5</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="21">
+    <row r="34" spans="1:4" ht="21">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="21">
+    <row r="35" spans="1:4" ht="21">
       <c r="A35" s="5" t="s">
         <v>5</v>
       </c>
@@ -2259,7 +2265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="21">
+    <row r="36" spans="1:4" ht="21">
       <c r="A36" s="5" t="s">
         <v>5</v>
       </c>
@@ -2270,7 +2276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="21">
+    <row r="37" spans="1:4" ht="21">
       <c r="A37" s="5" t="s">
         <v>5</v>
       </c>
@@ -2281,7 +2287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="21">
+    <row r="38" spans="1:4" ht="21">
       <c r="A38" s="5" t="s">
         <v>5</v>
       </c>
@@ -2292,7 +2298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="21">
+    <row r="39" spans="1:4" ht="21">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
@@ -2303,7 +2309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="21">
+    <row r="40" spans="1:4" ht="21">
       <c r="A40" s="5" t="s">
         <v>5</v>
       </c>
@@ -2313,8 +2319,11 @@
       <c r="C40" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="21">
+      <c r="D40" s="10" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="21">
       <c r="A41" s="5" t="s">
         <v>5</v>
       </c>
@@ -2324,21 +2333,24 @@
       <c r="C41" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="21">
+      <c r="D41" s="10" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="21">
       <c r="B42" s="7"/>
       <c r="C42" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="21">
+    <row r="43" spans="1:4" ht="21">
       <c r="A43" s="5"/>
       <c r="B43" s="7"/>
       <c r="C43" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="21">
+    <row r="44" spans="1:4" ht="21">
       <c r="A44" s="8" t="s">
         <v>42</v>
       </c>
@@ -2349,7 +2361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="21">
+    <row r="45" spans="1:4" ht="21">
       <c r="A45" s="8" t="s">
         <v>42</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="21">
+    <row r="46" spans="1:4" ht="21">
       <c r="A46" s="8" t="s">
         <v>42</v>
       </c>
@@ -2371,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="21">
+    <row r="47" spans="1:4" ht="21">
       <c r="A47" s="8" t="s">
         <v>42</v>
       </c>
@@ -2382,7 +2394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="21">
+    <row r="48" spans="1:4" ht="21">
       <c r="A48" s="8" t="s">
         <v>42</v>
       </c>
@@ -3063,7 +3075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="21">
+    <row r="113" spans="1:4" ht="21">
       <c r="A113" s="5" t="s">
         <v>97</v>
       </c>
@@ -3074,7 +3086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="21">
+    <row r="114" spans="1:4" ht="21">
       <c r="A114" s="5" t="s">
         <v>97</v>
       </c>
@@ -3085,7 +3097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="21">
+    <row r="115" spans="1:4" ht="21">
       <c r="A115" s="5" t="s">
         <v>97</v>
       </c>
@@ -3096,7 +3108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="21">
+    <row r="116" spans="1:4" ht="21">
       <c r="A116" s="5" t="s">
         <v>97</v>
       </c>
@@ -3107,7 +3119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="21">
+    <row r="117" spans="1:4" ht="21">
       <c r="A117" s="5" t="s">
         <v>97</v>
       </c>
@@ -3118,7 +3130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="21">
+    <row r="118" spans="1:4" ht="21">
       <c r="A118" s="5" t="s">
         <v>97</v>
       </c>
@@ -3129,7 +3141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="21">
+    <row r="119" spans="1:4" ht="21">
       <c r="A119" s="5" t="s">
         <v>97</v>
       </c>
@@ -3140,7 +3152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="21">
+    <row r="120" spans="1:4" ht="21">
       <c r="A120" s="5" t="s">
         <v>97</v>
       </c>
@@ -3151,7 +3163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="21">
+    <row r="121" spans="1:4" ht="21">
       <c r="A121" s="5" t="s">
         <v>97</v>
       </c>
@@ -3162,7 +3174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="21">
+    <row r="122" spans="1:4" ht="21">
       <c r="A122" s="5" t="s">
         <v>97</v>
       </c>
@@ -3173,7 +3185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="21">
+    <row r="123" spans="1:4" ht="21">
       <c r="A123" s="5" t="s">
         <v>97</v>
       </c>
@@ -3183,8 +3195,11 @@
       <c r="C123" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" ht="21">
+      <c r="D123" s="10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="21">
       <c r="A124" s="5" t="s">
         <v>97</v>
       </c>
@@ -3195,7 +3210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="21">
+    <row r="125" spans="1:4" ht="21">
       <c r="A125" s="5" t="s">
         <v>97</v>
       </c>
@@ -3206,7 +3221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="21">
+    <row r="126" spans="1:4" ht="21">
       <c r="A126" s="5" t="s">
         <v>97</v>
       </c>
@@ -3217,7 +3232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="21">
+    <row r="127" spans="1:4" ht="21">
       <c r="A127" s="5" t="s">
         <v>97</v>
       </c>
@@ -3228,7 +3243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="21">
+    <row r="128" spans="1:4" ht="21">
       <c r="A128" s="5" t="s">
         <v>97</v>
       </c>
@@ -7414,8 +7429,11 @@
     <hyperlink ref="D6" r:id="rId447" xr:uid="{832C304F-42C4-4027-86CB-79D37446D124}"/>
     <hyperlink ref="D8" r:id="rId448" xr:uid="{7DC15024-9F8C-4C66-8DF7-E26F989E0FAB}"/>
     <hyperlink ref="D9" r:id="rId449" xr:uid="{CE414B70-7490-4385-A15A-4CC404B38AF4}"/>
+    <hyperlink ref="D40" r:id="rId450" xr:uid="{85C5C607-9D47-4D0B-951F-68D011AAE9D0}"/>
+    <hyperlink ref="D41" r:id="rId451" xr:uid="{F191FAD4-4A81-4ECA-B80C-F84D52C1D49E}"/>
+    <hyperlink ref="D123" r:id="rId452" xr:uid="{10F54EF5-7EBE-47E4-B7FF-1E78A725D41E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId450"/>
+  <pageSetup orientation="portrait" r:id="rId453"/>
 </worksheet>
 </file>